--- a/reports/devops-juniors-israel-2026-W40.xlsx
+++ b/reports/devops-juniors-israel-2026-W40.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28T13:43:58</t>
+    <t xml:space="preserve">2026-09-29T12:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -351,6 +352,24 @@
     <t xml:space="preserve">2026-09-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -375,9 +394,6 @@
     <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -483,6 +499,21 @@
     <t xml:space="preserve">2026-09-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
@@ -507,6 +538,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -534,24 +583,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -687,28 +718,28 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -911,7 +942,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -919,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -927,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -935,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10">
@@ -1033,7 +1064,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1041,7 +1072,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1075,7 +1106,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1083,7 +1114,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1543,10 +1574,10 @@
         <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>115</v>
@@ -1575,10 +1606,10 @@
         <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>121</v>
@@ -1590,7 +1621,7 @@
         <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -1598,31 +1629,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1630,10 +1661,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>53</v>
@@ -1642,19 +1673,19 @@
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1662,13 +1693,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1677,16 +1708,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1700,13 +1731,13 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>138</v>
@@ -1732,25 +1763,25 @@
         <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -1758,13 +1789,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1773,16 +1804,16 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1790,19 +1821,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>153</v>
@@ -1822,19 +1853,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>158</v>
@@ -1846,7 +1877,7 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1854,31 +1885,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25">
@@ -1886,31 +1917,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1918,31 +1949,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1995,7 +2026,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2010,22 +2041,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -2048,7 +2079,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2060,7 +2091,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2083,7 +2114,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2095,7 +2126,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2118,7 +2149,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2130,7 +2161,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2153,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2165,7 +2196,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -2188,7 +2219,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2200,7 +2231,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -2223,7 +2254,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2235,7 +2266,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -2258,7 +2289,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2270,7 +2301,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2293,7 +2324,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2305,7 +2336,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -2328,7 +2359,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2340,7 +2371,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2394,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2375,7 +2406,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2429,7 @@
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2410,7 +2441,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -2433,7 +2464,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2445,7 +2476,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2459,16 +2490,16 @@
         <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2480,7 +2511,7 @@
         <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2494,16 +2525,16 @@
         <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,53 +2543,53 @@
         <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="K15" s="3">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
@@ -2567,36 +2598,36 @@
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2605,22 +2636,22 @@
         <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -2631,19 +2662,19 @@
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2655,7 +2686,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2666,42 +2697,42 @@
         <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="K20" s="3">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,45 +2741,45 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>153</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
@@ -2760,30 +2791,30 @@
         <v>155</v>
       </c>
       <c r="K22" s="3">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2792,246 +2823,246 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="K24" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="K25" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="K26" s="3">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="K28" s="3">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="K29" s="3">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>195</v>
@@ -3040,7 +3071,7 @@
         <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3051,31 +3082,31 @@
         <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K31" s="3">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -3089,7 +3120,7 @@
         <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
         <v>4</v>
@@ -3098,10 +3129,10 @@
         <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>205</v>
@@ -3110,7 +3141,7 @@
         <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
@@ -3121,50 +3152,54 @@
         <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
@@ -3176,11 +3211,77 @@
         <v>216</v>
       </c>
       <c r="K34" s="3">
-        <v>54</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K35" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="3">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3215,11 +3316,103 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3">
+        <v>41</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -3229,185 +3422,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3420,10 +3613,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -3434,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -3445,7 +3638,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -3453,10 +3646,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
@@ -3464,10 +3657,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
@@ -3478,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
@@ -3489,14 +3682,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3510,13 +3703,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2">
@@ -3524,10 +3717,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3539,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3551,7 +3744,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W40.xlsx
+++ b/reports/devops-juniors-israel-2026-W40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29T12:41:46</t>
+    <t xml:space="preserve">2026-09-30T12:27:48</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,7 +187,415 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
     <t xml:space="preserve">SAP</t>
@@ -196,262 +604,91 @@
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4472436545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
@@ -460,261 +697,48 @@
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC 243952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-243952-at-experis-4469770052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -727,37 +751,49 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -766,22 +802,10 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -815,9 +839,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -942,7 +963,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -950,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -958,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -966,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10">
@@ -1048,7 +1069,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1106,7 +1127,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1133,7 +1154,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1251,25 +1272,25 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1277,10 +1298,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1292,16 +1313,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1315,25 +1336,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1347,25 +1368,25 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1382,22 +1403,22 @@
         <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1405,19 +1426,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1429,7 +1450,7 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1437,31 +1458,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>68</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1469,31 +1490,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1501,31 +1522,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="3">
-        <v>46</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1533,31 +1554,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1565,31 +1586,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="3">
-        <v>41</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1597,31 +1618,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -1629,31 +1650,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>44</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1661,31 +1682,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3">
+        <v>41</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>36</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1693,19 +1714,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1717,7 +1738,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -1725,31 +1746,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1763,13 +1784,13 @@
         <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>143</v>
@@ -1789,31 +1810,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1821,31 +1842,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1853,31 +1874,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1885,31 +1906,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>24</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3">
-        <v>20</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25">
@@ -1917,31 +1938,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1949,31 +1970,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2011,7 +2032,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -2026,7 +2047,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2041,22 +2062,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2079,7 +2100,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2091,7 +2112,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2114,7 +2135,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2126,7 +2147,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2137,39 +2158,39 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K4" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2181,22 +2202,22 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K5" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2207,31 +2228,31 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K6" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2242,31 +2263,31 @@
         <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>80</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>70</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K7" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2280,51 +2301,51 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K8" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2333,313 +2354,313 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>47</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K10" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K11" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="K12" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>47</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3">
-        <v>41</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="K15" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K16" s="3">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>36</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K17" s="3">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2648,45 +2669,45 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="K18" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -2697,19 +2718,19 @@
         <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2721,74 +2742,74 @@
         <v>145</v>
       </c>
       <c r="K20" s="3">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="K21" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
         <v>41</v>
@@ -2796,293 +2817,293 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="K23" s="3">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="3">
-        <v>20</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>23</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>12</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K25" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="K26" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K28" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="K29" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="K30" s="3">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3091,33 +3112,33 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3126,33 +3147,33 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>28</v>
@@ -3161,33 +3182,33 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K33" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3196,33 +3217,33 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K34" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3232,56 +3253,89 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K35" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
         <v>0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K36" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K36" s="3">
-        <v>55</v>
+      <c r="I37" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K37" s="3">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K37"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3318,6 +3372,7 @@
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
     <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3325,8 +3380,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3348,10 +3403,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3359,55 +3414,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3">
+        <v>74</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3415,185 +3542,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3613,10 +3740,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -3624,10 +3751,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
@@ -3638,7 +3765,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
@@ -3649,7 +3776,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
@@ -3660,7 +3787,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
@@ -3671,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -3682,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3703,13 +3830,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2">
@@ -3720,7 +3847,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3729,10 +3856,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3744,7 +3871,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W40.xlsx
+++ b/reports/devops-juniors-israel-2026-W40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30T12:27:48</t>
+    <t xml:space="preserve">2026-10-01T13:03:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,6 +187,24 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -199,39 +217,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -310,21 +313,6 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -337,24 +325,6 @@
     <t xml:space="preserve">2026-08-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -373,126 +343,114 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
+    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -535,6 +493,45 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -553,42 +550,12 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">COM-C-TECH LTD</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory, Windows Server</t>
   </si>
   <si>
@@ -598,12 +565,6 @@
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any), Automation</t>
   </si>
   <si>
@@ -643,7 +604,7 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Power Control System Engineer</t>
@@ -691,154 +652,142 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -963,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -971,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -979,7 +928,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -987,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1018,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1077,7 +1026,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1085,7 +1034,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1127,7 +1076,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1154,7 +1103,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1272,25 +1221,25 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1298,10 +1247,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1313,16 +1262,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1354,7 +1303,7 @@
         <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1362,10 +1311,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>53</v>
@@ -1377,16 +1326,16 @@
         <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1394,13 +1343,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1409,16 +1358,16 @@
         <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -1426,13 +1375,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1441,16 +1390,16 @@
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1458,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1473,16 +1422,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1490,10 +1439,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>53</v>
@@ -1505,16 +1454,16 @@
         <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1522,31 +1471,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1557,28 +1506,28 @@
         <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1586,31 +1535,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1618,31 +1567,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -1650,31 +1599,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1688,25 +1637,25 @@
         <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>36</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3">
-        <v>41</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -1714,31 +1663,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1746,31 +1695,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>39</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1778,31 +1727,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1810,31 +1759,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1842,31 +1791,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1880,25 +1829,25 @@
         <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
@@ -1906,31 +1855,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -1944,13 +1893,13 @@
         <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>165</v>
@@ -1962,7 +1911,7 @@
         <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
@@ -1970,31 +1919,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +1981,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -2047,7 +1996,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2062,22 +2011,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2100,7 +2049,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2112,7 +2061,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2135,7 +2084,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2147,7 +2096,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2158,39 +2107,39 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2202,22 +2151,22 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2189,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2249,18 +2198,18 @@
         <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>53</v>
@@ -2272,33 +2221,33 @@
         <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2307,33 +2256,33 @@
         <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2342,33 +2291,33 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2377,30 +2326,30 @@
         <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>53</v>
@@ -2412,57 +2361,57 @@
         <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -2470,139 +2419,139 @@
         <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -2613,206 +2562,206 @@
         <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>36</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="3">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>39</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K19" s="3">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="K20" s="3">
-        <v>79</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="K21" s="3">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K22" s="3">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -2823,66 +2772,66 @@
         <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="K23" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="K24" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2893,19 +2842,19 @@
         <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2914,428 +2863,325 @@
         <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="K25" s="3">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="K26" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="3">
-        <v>10</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K29" s="3">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K30" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>8</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K33" s="3">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K34" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K35" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K36" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="K37" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3370,9 +3216,6 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3380,11 +3223,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3403,10 +3246,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3414,127 +3257,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>84</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>74</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>52</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3542,185 +3289,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3740,10 +3487,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
@@ -3751,10 +3498,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -3762,10 +3509,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -3773,10 +3520,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -3787,7 +3534,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -3798,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
@@ -3809,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3830,13 +3577,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3847,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3856,10 +3603,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3871,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W40.xlsx
+++ b/reports/devops-juniors-israel-2026-W40.xlsx
@@ -5,16 +5,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
-    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
-    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
-    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
+    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
+    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01T13:03:03</t>
+    <t xml:space="preserve">2026-10-02T12:24:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -493,6 +492,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -517,6 +531,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -532,36 +564,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -676,13 +678,13 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
@@ -920,7 +922,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +1036,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1042,7 +1044,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1861,13 +1863,13 @@
         <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
@@ -1879,7 +1881,7 @@
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -1887,13 +1889,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1902,16 +1904,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -1919,31 +1921,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2061,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2096,7 +2098,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2131,7 +2133,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -2166,7 +2168,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -2201,7 +2203,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2236,7 +2238,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -2271,7 +2273,7 @@
         <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2306,7 +2308,7 @@
         <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -2341,7 +2343,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -2376,7 +2378,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -2411,7 +2413,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -2446,7 +2448,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2481,7 +2483,7 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2516,7 +2518,7 @@
         <v>120</v>
       </c>
       <c r="K15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2551,7 +2553,7 @@
         <v>62</v>
       </c>
       <c r="K16" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -2586,7 +2588,7 @@
         <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -2621,7 +2623,7 @@
         <v>62</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -2656,7 +2658,7 @@
         <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -2691,7 +2693,7 @@
         <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2726,7 +2728,7 @@
         <v>148</v>
       </c>
       <c r="K21" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -2761,7 +2763,7 @@
         <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -2796,7 +2798,7 @@
         <v>114</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2807,13 +2809,13 @@
         <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
@@ -2828,21 +2830,21 @@
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2851,7 +2853,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>177</v>
@@ -2860,48 +2862,48 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="K26" s="3">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -2912,36 +2914,36 @@
         <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>58</v>
@@ -2956,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>177</v>
@@ -2965,24 +2967,24 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2991,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>177</v>
@@ -3000,24 +3002,24 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3026,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>177</v>
@@ -3035,21 +3037,21 @@
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>141</v>
@@ -3061,7 +3063,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>177</v>
@@ -3070,24 +3072,24 @@
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3096,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>177</v>
@@ -3105,24 +3107,24 @@
         <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K32" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3138,24 +3140,24 @@
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K33" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3171,13 +3173,13 @@
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K34" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3223,72 +3225,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="3">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G2"/>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-  </hyperlinks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3296,21 +3232,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>221</v>
@@ -3318,163 +3254,163 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3487,10 +3423,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
@@ -3501,7 +3437,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -3512,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -3520,10 +3456,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -3531,10 +3467,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -3545,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
@@ -3556,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3577,13 +3513,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -3594,7 +3530,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3606,7 +3542,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3618,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W40.xlsx
+++ b/reports/devops-juniors-israel-2026-W40.xlsx
@@ -5,15 +5,16 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
-    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
+    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
+    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
+    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
+    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02T12:24:05</t>
+    <t xml:space="preserve">2026-10-04T12:16:13</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -360,24 +361,6 @@
     <t xml:space="preserve">2026-09-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -492,15 +475,21 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
   </si>
   <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
   </si>
   <si>
@@ -519,199 +508,202 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dundee, Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4978622101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -922,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -930,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -938,7 +930,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -1020,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1036,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1044,7 +1036,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1575,25 +1567,25 @@
         <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>39</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>40</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1601,31 +1593,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>36</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1633,10 +1625,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>53</v>
@@ -1645,19 +1637,19 @@
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1665,31 +1657,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1706,10 +1698,10 @@
         <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>136</v>
@@ -1729,13 +1721,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1744,16 +1736,16 @@
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -1761,31 +1753,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1793,31 +1785,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
@@ -1825,13 +1817,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1840,16 +1832,16 @@
         <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
@@ -1857,10 +1849,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>111</v>
@@ -1872,16 +1864,16 @@
         <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -1889,10 +1881,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>105</v>
@@ -1904,13 +1896,13 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>72</v>
@@ -1921,31 +1913,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +1990,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2013,22 +2005,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
@@ -2051,7 +2043,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2063,7 +2055,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2086,7 +2078,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2098,7 +2090,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2121,7 +2113,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2133,7 +2125,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2156,7 +2148,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2168,7 +2160,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -2191,7 +2183,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2203,7 +2195,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2226,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2238,7 +2230,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -2261,7 +2253,7 @@
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2273,7 +2265,7 @@
         <v>72</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2296,7 +2288,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2308,7 +2300,7 @@
         <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -2331,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
@@ -2343,7 +2335,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -2366,7 +2358,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2378,7 +2370,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -2401,7 +2393,7 @@
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2413,7 +2405,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2436,7 +2428,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2448,7 +2440,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2471,7 +2463,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2483,7 +2475,7 @@
         <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2494,74 +2486,74 @@
         <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="K15" s="3">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>36</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K16" s="3">
-        <v>43</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
@@ -2570,60 +2562,60 @@
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="3">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -2637,16 +2629,16 @@
         <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
@@ -2658,18 +2650,18 @@
         <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2678,103 +2670,103 @@
         <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K20" s="3">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K21" s="3">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="K22" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>27</v>
@@ -2783,30 +2775,30 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K23" s="3">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>111</v>
@@ -2818,30 +2810,30 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K24" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>105</v>
@@ -2853,89 +2845,89 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>12</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K26" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="K27" s="3">
         <v>39</v>
@@ -2943,7 +2935,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>58</v>
@@ -2958,33 +2950,33 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>108</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -2993,33 +2985,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K29" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
@@ -3028,33 +3020,33 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>28</v>
@@ -3063,33 +3055,33 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3098,33 +3090,33 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K32" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3134,30 +3126,30 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K33" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3167,19 +3159,19 @@
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K34" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3225,6 +3217,72 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="41" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3232,185 +3290,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3423,10 +3481,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2">
@@ -3434,10 +3492,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -3448,7 +3506,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -3456,10 +3514,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -3467,10 +3525,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
@@ -3481,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -3492,14 +3550,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3513,13 +3571,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2">
@@ -3530,7 +3588,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3542,7 +3600,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3554,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3"/>
     </row>
